--- a/data/trans_orig/P1405-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1405-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colitis en 2012</t>
+          <t>Población con diagnóstico de colitis en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16976</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22468</t>
+          <t>22560</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282555</t>
+          <t>282727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293778</t>
+          <t>293839</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270269</t>
+          <t>270964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283449</t>
+          <t>284000</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559515</t>
+          <t>559423</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575883</t>
+          <t>575933</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>11684</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16745</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23409</t>
+          <t>22406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493961</t>
+          <t>493843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503456</t>
+          <t>503449</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507020</t>
+          <t>507214</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>519635</t>
+          <t>519633</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1005883</t>
+          <t>1006886</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021590</t>
+          <t>1021802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15570</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316824</t>
+          <t>317538</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328343</t>
+          <t>328364</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338874</t>
+          <t>338830</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649496</t>
+          <t>649437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>661140</t>
+          <t>661166</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,47 +1810,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>9852</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>4759</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>17816</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>9852</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>4992</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>18640</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>371901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373982</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>369321</t>
+          <t>370773</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383918</t>
+          <t>384309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,47 +1923,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>753081</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>745117</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>758174</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>98,71%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>753081</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>744293</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>757941</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>975</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>8944</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19098</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21608</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203427</t>
+          <t>203674</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211633</t>
+          <t>211643</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199662</t>
+          <t>200493</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215190</t>
+          <t>215388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410601</t>
+          <t>410494</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425335</t>
+          <t>425318</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13993</t>
+          <t>13970</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266132</t>
+          <t>264633</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273007</t>
+          <t>273009</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>268243</t>
+          <t>268382</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277113</t>
+          <t>277128</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538084</t>
+          <t>538107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549127</t>
+          <t>549109</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17332</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18014</t>
+          <t>17950</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29908</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>645456</t>
+          <t>644754</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>659807</t>
+          <t>659673</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>675839</t>
+          <t>675903</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689019</t>
+          <t>689656</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1326733</t>
+          <t>1326794</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1346363</t>
+          <t>1347055</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15546</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18522</t>
+          <t>18525</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>769703</t>
+          <t>770599</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>778076</t>
+          <t>778080</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>805849</t>
+          <t>805490</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>819254</t>
+          <t>819262</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1581971</t>
+          <t>1581968</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1596231</t>
+          <t>1596258</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>18935</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42085</t>
+          <t>42327</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>47824</t>
+          <t>46485</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80268</t>
+          <t>79684</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>73653</t>
+          <t>71252</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113629</t>
+          <t>110948</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3384694</t>
+          <t>3384452</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3407653</t>
+          <t>3407844</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3473648</t>
+          <t>3474232</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3506092</t>
+          <t>3507431</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6867065</t>
+          <t>6869746</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6907041</t>
+          <t>6909442</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colitis en 2016</t>
+          <t>Población con diagnóstico de colitis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13020</t>
+          <t>12421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14544</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,47 +4104,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>12470</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>6408</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>20984</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>12470</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>6896</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>23531</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>280741</t>
+          <t>281340</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292322</t>
+          <t>292661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274159</t>
+          <t>274172</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285540</t>
+          <t>285905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,47 +4217,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>569994</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>561480</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>576056</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>98,9%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>569994</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>558933</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>575568</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>97,86%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>10271</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>12004</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496084</t>
+          <t>495357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513228</t>
+          <t>512813</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522101</t>
+          <t>522082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1013764</t>
+          <t>1013655</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023640</t>
+          <t>1023659</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7779</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>10191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310786</t>
+          <t>310750</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317701</t>
+          <t>317706</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329327</t>
+          <t>329726</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643651</t>
+          <t>644683</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653014</t>
+          <t>653018</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21501</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>21470</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>364612</t>
+          <t>365020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>365782</t>
+          <t>366716</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>381209</t>
+          <t>381304</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>735760</t>
+          <t>735777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750844</t>
+          <t>751130</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208088</t>
+          <t>207680</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217539</t>
+          <t>217531</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>419462</t>
+          <t>420169</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428685</t>
+          <t>428755</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16529</t>
+          <t>15424</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253126</t>
+          <t>254077</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261265</t>
+          <t>262283</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271848</t>
+          <t>271847</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>519709</t>
+          <t>520814</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533149</t>
+          <t>533170</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20563</t>
+          <t>20466</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24980</t>
+          <t>24919</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>646388</t>
+          <t>646088</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655498</t>
+          <t>655473</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>670731</t>
+          <t>670828</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>684848</t>
+          <t>684893</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1322872</t>
+          <t>1322933</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1339048</t>
+          <t>1339042</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>15803</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18426</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28919</t>
+          <t>29472</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>763379</t>
+          <t>762780</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775819</t>
+          <t>775835</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>807741</t>
+          <t>806844</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>821158</t>
+          <t>820703</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1575831</t>
+          <t>1575278</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1594489</t>
+          <t>1594495</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16236</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40427</t>
+          <t>37674</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41414</t>
+          <t>41740</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>72720</t>
+          <t>73977</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,47 +6848,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>81136</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>62648</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>100946</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>81136</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>64884</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>99993</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3353923</t>
+          <t>3356676</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3378114</t>
+          <t>3378612</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3471822</t>
+          <t>3470565</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3503128</t>
+          <t>3502802</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,47 +6961,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6496</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6857756</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6837946</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6876244</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>98,83%</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6496</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6857756</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6838899</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6874008</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1405-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1405-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12011</t>
+          <t>11612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16281</t>
+          <t>17429</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22560</t>
+          <t>22138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282727</t>
+          <t>283126</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293839</t>
+          <t>293832</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270964</t>
+          <t>269816</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284000</t>
+          <t>283920</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559423</t>
+          <t>559845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575933</t>
+          <t>575843</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16551</t>
+          <t>17803</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22406</t>
+          <t>24403</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493843</t>
+          <t>494844</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503449</t>
+          <t>503452</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507214</t>
+          <t>505962</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>519633</t>
+          <t>519369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1006886</t>
+          <t>1004889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021802</t>
+          <t>1020871</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15629</t>
+          <t>14666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317538</t>
+          <t>317597</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328364</t>
+          <t>328225</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338830</t>
+          <t>338854</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649437</t>
+          <t>650400</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>661166</t>
+          <t>661112</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>18894</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>18683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>370773</t>
+          <t>370057</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>384309</t>
+          <t>383894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>745117</t>
+          <t>744250</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>758174</t>
+          <t>758169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19098</t>
+          <t>18004</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>21804</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203674</t>
+          <t>203529</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211643</t>
+          <t>211639</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200493</t>
+          <t>201587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215388</t>
+          <t>214956</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410494</t>
+          <t>410405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425318</t>
+          <t>425289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264633</t>
+          <t>264905</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273009</t>
+          <t>273002</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>268382</t>
+          <t>268323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277128</t>
+          <t>277105</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538107</t>
+          <t>538139</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549109</t>
+          <t>549114</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17950</t>
+          <t>17863</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>644754</t>
+          <t>646300</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>659673</t>
+          <t>659640</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>675903</t>
+          <t>675990</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689656</t>
+          <t>689819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1326794</t>
+          <t>1326888</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1347055</t>
+          <t>1346711</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15905</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18525</t>
+          <t>19194</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>770599</t>
+          <t>770635</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>778080</t>
+          <t>778079</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>805490</t>
+          <t>806231</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>819262</t>
+          <t>819241</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1581968</t>
+          <t>1581299</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1596258</t>
+          <t>1596271</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42327</t>
+          <t>42315</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>46485</t>
+          <t>47695</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>79684</t>
+          <t>81547</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,47 +3525,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>91495</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>72854</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>113983</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>91495</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>71252</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>110948</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3384452</t>
+          <t>3384464</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3407844</t>
+          <t>3407972</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3474232</t>
+          <t>3472369</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3507431</t>
+          <t>3506221</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,47 +3638,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6423</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6889199</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6866711</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6907840</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6423</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6889199</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6869746</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6909442</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12421</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6408</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20984</t>
+          <t>21197</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281340</t>
+          <t>279910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292661</t>
+          <t>292334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274172</t>
+          <t>274170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285905</t>
+          <t>285547</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561480</t>
+          <t>561267</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>576056</t>
+          <t>575926</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>962</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10271</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>495357</t>
+          <t>495391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512813</t>
+          <t>514352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522082</t>
+          <t>522122</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1013655</t>
+          <t>1011913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023659</t>
+          <t>1022802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7815</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310750</t>
+          <t>310773</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329726</t>
+          <t>328741</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644683</t>
+          <t>644090</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653018</t>
+          <t>653005</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5103,42 +5103,42 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>11505</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5185</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21225</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>1,34%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11505</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5979</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20567</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21470</t>
+          <t>22774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>365020</t>
+          <t>365041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5211,49 +5211,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>98,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>375778</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>366058</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>382098</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,52%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>98,66%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>375778</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>366716</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>381304</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,69%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>701</t>
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>735777</t>
+          <t>734473</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>751130</t>
+          <t>750778</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207680</t>
+          <t>207916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217531</t>
+          <t>217535</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>420169</t>
+          <t>419415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428755</t>
+          <t>428769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>11636</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15424</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254077</t>
+          <t>254269</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262283</t>
+          <t>261479</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271847</t>
+          <t>271430</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>520814</t>
+          <t>518994</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533170</t>
+          <t>533402</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>21421</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24919</t>
+          <t>25687</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>646088</t>
+          <t>645977</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655473</t>
+          <t>655455</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>670828</t>
+          <t>669873</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>684893</t>
+          <t>684659</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1322933</t>
+          <t>1322165</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1339042</t>
+          <t>1338365</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>15969</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29472</t>
+          <t>28112</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762780</t>
+          <t>762614</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775835</t>
+          <t>775818</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>806844</t>
+          <t>808434</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>820703</t>
+          <t>821643</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1575278</t>
+          <t>1576638</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1594495</t>
+          <t>1594954</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37674</t>
+          <t>37841</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41740</t>
+          <t>42015</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>73977</t>
+          <t>73727</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62648</t>
+          <t>65212</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100946</t>
+          <t>102598</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3356676</t>
+          <t>3356509</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3378612</t>
+          <t>3377888</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3470565</t>
+          <t>3470815</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3502802</t>
+          <t>3502527</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6837946</t>
+          <t>6836294</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6876244</t>
+          <t>6873680</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
